--- a/AAII_Financials/Quarterly/KAVL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KAVL_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="92">
   <si>
     <t>KAVL</t>
   </si>
@@ -656,250 +656,263 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E7" s="2">
         <v>45138</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44957</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44865</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44592</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44316</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44135</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44043</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43951</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43861</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43769</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>58800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>18100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>37400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>32400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>22500</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E9" s="3">
         <v>2300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>46800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>11900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>32600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>28000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>20000</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>900</v>
+      </c>
+      <c r="E10" s="3">
         <v>1300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1100</v>
-      </c>
-      <c r="H10" s="3">
-        <v>400</v>
       </c>
       <c r="I10" s="3">
         <v>400</v>
       </c>
       <c r="J10" s="3">
+        <v>400</v>
+      </c>
+      <c r="K10" s="3">
         <v>-700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>12000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2500</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -919,8 +932,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -972,8 +986,11 @@
       <c r="S12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1025,8 +1042,11 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1078,8 +1098,11 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1131,8 +1154,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1149,114 +1175,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E17" s="3">
         <v>5200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>69200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>22200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>36900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>29400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>20400</v>
       </c>
-      <c r="R17" s="3">
-        <v>0</v>
-      </c>
       <c r="S17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-4000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-10400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2100</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1276,17 +1309,18 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-200</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
@@ -1323,29 +1357,32 @@
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>4</v>
+      <c r="R20" s="3">
+        <v>0</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-4000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3000</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1358,32 +1395,35 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3">
         <v>-3400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-4100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>400</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3">
         <v>2900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2100</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1435,61 +1475,67 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-10500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4100</v>
-      </c>
-      <c r="N23" s="3">
-        <v>400</v>
       </c>
       <c r="O23" s="3">
         <v>400</v>
       </c>
       <c r="P23" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q23" s="3">
         <v>2900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2100</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
       <c r="S23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1515,34 +1561,37 @@
         <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>-1400</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1000</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1594,114 +1643,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1100</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
       <c r="S26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1100</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
       <c r="S27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1753,8 +1811,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1806,8 +1867,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1859,8 +1923,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1912,17 +1979,20 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>400</v>
+      </c>
+      <c r="E32" s="3">
         <v>200</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
@@ -1959,67 +2029,73 @@
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>4</v>
+      <c r="R32" s="3">
+        <v>0</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-4000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-4300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1100</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
       <c r="S33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2071,119 +2147,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-4000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-4300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1100</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
       <c r="S35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E38" s="2">
         <v>45138</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44957</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44865</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44592</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44316</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44135</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44043</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43951</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43861</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43769</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2203,8 +2288,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2224,61 +2310,65 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>500</v>
+      </c>
+      <c r="E41" s="3">
         <v>1000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2000</v>
       </c>
-      <c r="R41" s="3">
-        <v>0</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S41" s="3">
+        <v>0</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2330,97 +2420,103 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E43" s="3">
         <v>1800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>18100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3200</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>3600</v>
+        <v>4100</v>
       </c>
       <c r="E44" s="3">
         <v>3600</v>
       </c>
       <c r="F44" s="3">
+        <v>3600</v>
+      </c>
+      <c r="G44" s="3">
         <v>3800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>9200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>14800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>18300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>14900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>28800</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
-      </c>
       <c r="O44" s="3">
         <v>0</v>
       </c>
@@ -2430,34 +2526,37 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>4</v>
+      <c r="R44" s="3">
+        <v>0</v>
       </c>
       <c r="S44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="E45" s="3">
         <v>200</v>
       </c>
       <c r="F45" s="3">
+        <v>200</v>
+      </c>
+      <c r="G45" s="3">
         <v>300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>500</v>
-      </c>
-      <c r="I45" s="3">
-        <v>400</v>
       </c>
       <c r="J45" s="3">
         <v>400</v>
@@ -2466,13 +2565,13 @@
         <v>400</v>
       </c>
       <c r="L45" s="3">
+        <v>400</v>
+      </c>
+      <c r="M45" s="3">
         <v>200</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>4</v>
+      <c r="N45" s="3">
+        <v>0</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>4</v>
@@ -2489,79 +2588,85 @@
       <c r="S45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E46" s="3">
         <v>6600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>17200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>23800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>30100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>23800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>49100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>14700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5200</v>
       </c>
-      <c r="R46" s="3">
-        <v>0</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S46" s="3">
+        <v>0</v>
+      </c>
+      <c r="T46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="E47" s="3">
         <v>1800</v>
       </c>
       <c r="F47" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G47" s="3">
         <v>1500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2200</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>4</v>
       </c>
@@ -2577,8 +2682,8 @@
       <c r="M47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -2595,19 +2700,22 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="E48" s="3">
         <v>1100</v>
       </c>
       <c r="F48" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="G48" s="3">
         <v>1200</v>
@@ -2616,10 +2724,10 @@
         <v>1200</v>
       </c>
       <c r="I48" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="J48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3">
         <v>100</v>
@@ -2636,8 +2744,8 @@
       <c r="O48" s="3">
         <v>100</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>4</v>
+      <c r="P48" s="3">
+        <v>100</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>4</v>
@@ -2648,17 +2756,20 @@
       <c r="S48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E49" s="3">
         <v>11700</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F49" s="3" t="s">
         <v>4</v>
       </c>
@@ -2674,8 +2785,8 @@
       <c r="J49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
+      <c r="K49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
@@ -2701,8 +2812,11 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2754,8 +2868,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2807,8 +2924,11 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2860,8 +2980,11 @@
       <c r="S52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2913,61 +3036,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E54" s="3">
         <v>21200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>17300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>23800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>30200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>49200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>9700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5200</v>
       </c>
-      <c r="R54" s="3">
-        <v>0</v>
-      </c>
       <c r="S54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2987,8 +3116,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3008,70 +3138,74 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E57" s="3">
         <v>2400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2400</v>
       </c>
-      <c r="G57" s="3">
-        <v>0</v>
-      </c>
       <c r="H57" s="3">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3">
         <v>900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>9300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>17100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>38300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2400</v>
       </c>
-      <c r="R57" s="3">
-        <v>0</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>800</v>
+      </c>
+      <c r="E58" s="3">
         <v>500</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F58" s="3" t="s">
         <v>4</v>
       </c>
@@ -3087,8 +3221,8 @@
       <c r="J58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -3114,8 +3248,11 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3123,105 +3260,111 @@
         <v>1300</v>
       </c>
       <c r="E59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F59" s="3">
         <v>4100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>800</v>
-      </c>
-      <c r="I59" s="3">
-        <v>500</v>
       </c>
       <c r="J59" s="3">
         <v>500</v>
       </c>
       <c r="K59" s="3">
+        <v>500</v>
+      </c>
+      <c r="L59" s="3">
         <v>900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1400</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S59" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E60" s="3">
         <v>4300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>13800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>17500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>39900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2400</v>
       </c>
-      <c r="R60" s="3">
-        <v>0</v>
-      </c>
       <c r="S60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3273,8 +3416,11 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3282,19 +3428,19 @@
         <v>900</v>
       </c>
       <c r="E62" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="F62" s="3">
         <v>1000</v>
       </c>
       <c r="G62" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="H62" s="3">
         <v>1100</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="J62" s="3">
         <v>0</v>
@@ -3306,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="M62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N62" s="3">
         <v>100</v>
@@ -3314,8 +3460,8 @@
       <c r="O62" s="3">
         <v>100</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>4</v>
+      <c r="P62" s="3">
+        <v>100</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>4</v>
@@ -3326,8 +3472,11 @@
       <c r="S62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3379,8 +3528,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3432,8 +3584,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3485,61 +3640,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>5200</v>
+        <v>5800</v>
       </c>
       <c r="E66" s="3">
         <v>5200</v>
       </c>
       <c r="F66" s="3">
+        <v>5200</v>
+      </c>
+      <c r="G66" s="3">
         <v>4800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>17500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>39900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2400</v>
       </c>
-      <c r="R66" s="3">
-        <v>0</v>
-      </c>
       <c r="S66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3559,8 +3720,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3612,8 +3774,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3665,8 +3830,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3718,8 +3886,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3771,61 +3942,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-30800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-28400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-26600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-22600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-19600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-16900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-13100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-8000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-5300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-3600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2700</v>
-      </c>
-      <c r="R72" s="3">
-        <v>-100</v>
       </c>
       <c r="S72" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3877,8 +4054,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3930,8 +4110,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3983,61 +4166,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E76" s="3">
         <v>16000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2800</v>
       </c>
-      <c r="R76" s="3">
-        <v>0</v>
-      </c>
       <c r="S76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4089,119 +4278,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E80" s="2">
         <v>45138</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44957</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44865</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44592</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44316</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44135</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44043</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43951</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43861</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43769</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-4000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-4300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1100</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
       <c r="S81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4221,22 +4419,23 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>200</v>
+      </c>
+      <c r="E83" s="3">
         <v>100</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
       <c r="F83" s="3">
         <v>0</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>4</v>
+      <c r="G83" s="3">
+        <v>0</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>4</v>
@@ -4253,8 +4452,8 @@
       <c r="L83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -4274,8 +4473,11 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4327,8 +4529,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4380,8 +4585,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4433,8 +4641,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4486,8 +4697,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4539,61 +4753,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-9300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2000</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
       <c r="S89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4613,8 +4833,9 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4666,8 +4887,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4719,8 +4943,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4772,22 +4999,25 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>-300</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>4</v>
+      <c r="G94" s="3">
+        <v>0</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>4</v>
@@ -4804,8 +5034,8 @@
       <c r="L94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -4825,8 +5055,11 @@
       <c r="S94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4846,8 +5079,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4899,8 +5133,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4952,8 +5189,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5005,8 +5245,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5058,46 +5301,49 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E100" s="3">
         <v>500</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>1500</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>9700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>4</v>
+      <c r="O100" s="3">
+        <v>0</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>4</v>
@@ -5111,8 +5357,11 @@
       <c r="S100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5164,57 +5413,63 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2000</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KAVL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KAVL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
   <si>
     <t>KAVL</t>
   </si>
@@ -656,263 +656,276 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E7" s="2">
         <v>45230</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45138</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45046</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44957</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44865</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44773</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44681</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44592</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44500</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44408</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44316</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44227</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44135</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44043</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43951</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43861</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43769</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E8" s="3">
         <v>4000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>58800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>18100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>37400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>32400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>22500</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E9" s="3">
         <v>3100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>46800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>11900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>32600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>28000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>20000</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E10" s="3">
         <v>900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1100</v>
-      </c>
-      <c r="I10" s="3">
-        <v>400</v>
       </c>
       <c r="J10" s="3">
         <v>400</v>
       </c>
       <c r="K10" s="3">
+        <v>400</v>
+      </c>
+      <c r="L10" s="3">
         <v>-700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>12000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2500</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,8 +946,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -989,8 +1003,11 @@
       <c r="T12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,31 +1062,34 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1101,31 +1121,34 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1157,8 +1180,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1202,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E17" s="3">
         <v>6000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>69200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>22200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>36900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>29400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>20400</v>
       </c>
-      <c r="S17" s="3">
-        <v>0</v>
-      </c>
       <c r="T17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-4000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-10400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2100</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,20 +1343,21 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-200</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
@@ -1360,32 +1394,35 @@
       <c r="R20" s="3">
         <v>0</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>4</v>
+      <c r="S20" s="3">
+        <v>0</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-4000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-3000</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1398,32 +1435,35 @@
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N21" s="3">
         <v>-3400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-4100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>400</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3">
         <v>2900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2100</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1478,64 +1518,70 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-10500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4100</v>
-      </c>
-      <c r="O23" s="3">
-        <v>400</v>
       </c>
       <c r="P23" s="3">
         <v>400</v>
       </c>
       <c r="Q23" s="3">
+        <v>400</v>
+      </c>
+      <c r="R23" s="3">
         <v>2900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2100</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
       <c r="T23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1564,34 +1610,37 @@
         <v>0</v>
       </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>-1400</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1000</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1100</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
       <c r="T26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-5000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1100</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
       <c r="T27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1872,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1931,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,20 +2049,23 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>300</v>
+      </c>
+      <c r="E32" s="3">
         <v>400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>200</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
@@ -2032,70 +2102,76 @@
       <c r="R32" s="3">
         <v>0</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>4</v>
+      <c r="S32" s="3">
+        <v>0</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-5000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1100</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
       <c r="T33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-5000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1100</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
       <c r="T35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E38" s="2">
         <v>45230</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45138</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45046</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44957</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44865</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44773</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44681</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44592</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44500</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44408</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44316</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44227</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44135</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44043</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43951</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43861</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43769</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,64 +2397,68 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>600</v>
+      </c>
+      <c r="E41" s="3">
         <v>500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2000</v>
       </c>
-      <c r="S41" s="3">
-        <v>0</v>
-      </c>
-      <c r="T41" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T41" s="3">
+        <v>0</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2423,103 +2513,109 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>700</v>
+      </c>
+      <c r="E43" s="3">
         <v>1900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>18100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>12700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3200</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E44" s="3">
         <v>4100</v>
-      </c>
-      <c r="E44" s="3">
-        <v>3600</v>
       </c>
       <c r="F44" s="3">
         <v>3600</v>
       </c>
       <c r="G44" s="3">
+        <v>3600</v>
+      </c>
+      <c r="H44" s="3">
         <v>3800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>9200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>14800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>18300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>14900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>28800</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
       <c r="P44" s="3">
         <v>0</v>
       </c>
@@ -2529,14 +2625,17 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>4</v>
+      <c r="S44" s="3">
+        <v>0</v>
       </c>
       <c r="T44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2544,22 +2643,22 @@
         <v>400</v>
       </c>
       <c r="E45" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F45" s="3">
         <v>200</v>
       </c>
       <c r="G45" s="3">
+        <v>200</v>
+      </c>
+      <c r="H45" s="3">
         <v>300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>500</v>
-      </c>
-      <c r="J45" s="3">
-        <v>400</v>
       </c>
       <c r="K45" s="3">
         <v>400</v>
@@ -2568,13 +2667,13 @@
         <v>400</v>
       </c>
       <c r="M45" s="3">
+        <v>400</v>
+      </c>
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="N45" s="3">
-        <v>0</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>4</v>
+      <c r="O45" s="3">
+        <v>0</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>4</v>
@@ -2591,85 +2690,91 @@
       <c r="T45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E46" s="3">
         <v>6900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>17200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>23800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>30100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>23800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>49100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>14700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5200</v>
       </c>
-      <c r="S46" s="3">
-        <v>0</v>
-      </c>
-      <c r="T46" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T46" s="3">
+        <v>0</v>
+      </c>
+      <c r="U46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E47" s="3">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="F47" s="3">
         <v>1800</v>
       </c>
       <c r="G47" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H47" s="3">
         <v>1500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2200</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
@@ -2685,8 +2790,8 @@
       <c r="N47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -2703,8 +2808,11 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2712,13 +2820,13 @@
         <v>1000</v>
       </c>
       <c r="E48" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="F48" s="3">
         <v>1100</v>
       </c>
       <c r="G48" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="H48" s="3">
         <v>1200</v>
@@ -2727,10 +2835,10 @@
         <v>1200</v>
       </c>
       <c r="J48" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="K48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3">
         <v>100</v>
@@ -2747,8 +2855,8 @@
       <c r="P48" s="3">
         <v>100</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>4</v>
+      <c r="Q48" s="3">
+        <v>100</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>4</v>
@@ -2759,20 +2867,23 @@
       <c r="T48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E49" s="3">
         <v>11500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11700</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G49" s="3" t="s">
         <v>4</v>
       </c>
@@ -2788,8 +2899,8 @@
       <c r="K49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
+      <c r="L49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -2815,8 +2926,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,8 +3044,11 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2983,8 +3103,11 @@
       <c r="T52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,64 +3162,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E54" s="3">
         <v>19400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>21200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>13000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>14100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>30200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>23900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>49200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>9700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5200</v>
       </c>
-      <c r="S54" s="3">
-        <v>0</v>
-      </c>
       <c r="T54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,64 +3269,68 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E57" s="3">
         <v>2800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2400</v>
       </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
       <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3">
         <v>900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>17100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>38300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2400</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
-      </c>
-      <c r="T57" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T57" s="3">
+        <v>0</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3204,11 +3338,11 @@
         <v>800</v>
       </c>
       <c r="E58" s="3">
+        <v>800</v>
+      </c>
+      <c r="F58" s="3">
         <v>500</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G58" s="3" t="s">
         <v>4</v>
       </c>
@@ -3224,8 +3358,8 @@
       <c r="K58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="L58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -3251,120 +3385,129 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="E59" s="3">
         <v>1300</v>
       </c>
       <c r="F59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G59" s="3">
         <v>4100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>800</v>
-      </c>
-      <c r="J59" s="3">
-        <v>500</v>
       </c>
       <c r="K59" s="3">
         <v>500</v>
       </c>
       <c r="L59" s="3">
+        <v>500</v>
+      </c>
+      <c r="M59" s="3">
         <v>900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1400</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T59" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E60" s="3">
         <v>5000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>17500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>39900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2400</v>
       </c>
-      <c r="S60" s="3">
-        <v>0</v>
-      </c>
       <c r="T60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3419,31 +3562,34 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="E62" s="3">
         <v>900</v>
       </c>
       <c r="F62" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="G62" s="3">
         <v>1000</v>
       </c>
       <c r="H62" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="I62" s="3">
         <v>1100</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -3455,7 +3601,7 @@
         <v>0</v>
       </c>
       <c r="N62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O62" s="3">
         <v>100</v>
@@ -3463,8 +3609,8 @@
       <c r="P62" s="3">
         <v>100</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>4</v>
+      <c r="Q62" s="3">
+        <v>100</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>4</v>
@@ -3475,8 +3621,11 @@
       <c r="T62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,64 +3798,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E66" s="3">
         <v>5800</v>
-      </c>
-      <c r="E66" s="3">
-        <v>5200</v>
       </c>
       <c r="F66" s="3">
         <v>5200</v>
       </c>
       <c r="G66" s="3">
+        <v>5200</v>
+      </c>
+      <c r="H66" s="3">
         <v>4800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>17500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>39900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2400</v>
       </c>
-      <c r="S66" s="3">
-        <v>0</v>
-      </c>
       <c r="T66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3889,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,64 +4116,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-32900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-30800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-28400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-26600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-22600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-19600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-16900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-13100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-8000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-5300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-3600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>4100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2700</v>
-      </c>
-      <c r="S72" s="3">
-        <v>-100</v>
       </c>
       <c r="T72" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,64 +4352,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E76" s="3">
         <v>13600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>16300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2800</v>
       </c>
-      <c r="S76" s="3">
-        <v>0</v>
-      </c>
       <c r="T76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E80" s="2">
         <v>45230</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45138</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45046</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44957</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44865</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44773</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44681</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44592</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44500</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44408</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44316</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44227</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44135</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44043</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43951</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43861</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43769</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-5000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1100</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
       <c r="T81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,8 +4618,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4429,16 +4628,16 @@
         <v>200</v>
       </c>
       <c r="E83" s="3">
+        <v>200</v>
+      </c>
+      <c r="F83" s="3">
         <v>100</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
       <c r="G83" s="3">
         <v>0</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>4</v>
+      <c r="H83" s="3">
+        <v>0</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>4</v>
@@ -4455,8 +4654,8 @@
       <c r="M83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
+      <c r="N83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O83" s="3">
         <v>0</v>
@@ -4476,8 +4675,11 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-9300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2000</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
       <c r="T89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,8 +5054,9 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4890,8 +5111,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,8 +5229,11 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5011,16 +5241,16 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-300</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>4</v>
+      <c r="H94" s="3">
+        <v>0</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>4</v>
@@ -5037,8 +5267,8 @@
       <c r="M94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
+      <c r="N94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O94" s="3">
         <v>0</v>
@@ -5058,8 +5288,11 @@
       <c r="T94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5313,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5136,8 +5370,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,49 +5547,52 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>500</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>1500</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>9700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>4</v>
+      <c r="P100" s="3">
+        <v>0</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>4</v>
@@ -5360,8 +5606,11 @@
       <c r="T100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5416,60 +5665,66 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-5500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>4800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2000</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
       <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KAVL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KAVL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
   <si>
     <t>KAVL</t>
   </si>
@@ -656,276 +656,288 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E7" s="2">
         <v>45322</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45230</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45138</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45046</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44957</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44865</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44773</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44681</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44592</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44500</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44408</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44316</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44227</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44135</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44043</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43951</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43861</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43769</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E8" s="3">
         <v>3200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>58800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>18100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>37400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>9400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>32400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>22500</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E9" s="3">
         <v>2000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>46800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>11900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>32600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>28000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>20000</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>500</v>
+      </c>
+      <c r="E10" s="3">
         <v>1200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1100</v>
-      </c>
-      <c r="J10" s="3">
-        <v>400</v>
       </c>
       <c r="K10" s="3">
         <v>400</v>
       </c>
       <c r="L10" s="3">
+        <v>400</v>
+      </c>
+      <c r="M10" s="3">
         <v>-700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>12000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2500</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -947,8 +959,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1006,8 +1019,11 @@
       <c r="U12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1065,17 +1081,20 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1091,8 +1110,8 @@
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1124,16 +1143,19 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
         <v>200</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>4</v>
+      <c r="E15" s="3">
+        <v>200</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>4</v>
@@ -1150,8 +1172,8 @@
       <c r="J15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
+      <c r="K15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1183,8 +1205,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,126 +1228,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E17" s="3">
         <v>5000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>69200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>22200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>36900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>29400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>20400</v>
       </c>
-      <c r="T17" s="3">
-        <v>0</v>
-      </c>
       <c r="U17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-4000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-10400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2100</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,23 +1376,24 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
@@ -1397,35 +1430,38 @@
       <c r="S20" s="3">
         <v>0</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>4</v>
+      <c r="T20" s="3">
+        <v>0</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-4000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-3000</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1438,32 +1474,35 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3">
         <v>-3400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-4100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>400</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3">
         <v>2900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2100</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1521,67 +1560,73 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-10500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4100</v>
-      </c>
-      <c r="P23" s="3">
-        <v>400</v>
       </c>
       <c r="Q23" s="3">
         <v>400</v>
       </c>
       <c r="R23" s="3">
+        <v>400</v>
+      </c>
+      <c r="S23" s="3">
         <v>2900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2100</v>
       </c>
-      <c r="T23" s="3">
-        <v>0</v>
-      </c>
       <c r="U23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1613,34 +1658,37 @@
         <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>-1400</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1000</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,126 +1746,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1100</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
       <c r="U26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1100</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
       <c r="U27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,8 +1932,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1934,8 +1994,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2056,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,23 +2118,26 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>200</v>
+      </c>
+      <c r="E32" s="3">
         <v>300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
@@ -2105,73 +2174,79 @@
       <c r="S32" s="3">
         <v>0</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>4</v>
+      <c r="T32" s="3">
+        <v>0</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1100</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
       <c r="U33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2304,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1100</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
       <c r="U35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E38" s="2">
         <v>45322</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45230</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45138</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45046</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44957</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44865</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44773</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44681</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44592</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44500</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44408</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44316</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44227</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44135</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44043</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43951</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43861</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43769</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2459,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,67 +2483,71 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>500</v>
+      </c>
+      <c r="E41" s="3">
         <v>600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2000</v>
       </c>
-      <c r="T41" s="3">
-        <v>0</v>
-      </c>
-      <c r="U41" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="U41" s="3">
+        <v>0</v>
+      </c>
+      <c r="V41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2516,8 +2605,11 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2525,100 +2617,103 @@
         <v>700</v>
       </c>
       <c r="E43" s="3">
+        <v>700</v>
+      </c>
+      <c r="F43" s="3">
         <v>1900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>18100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>12700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3200</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>600</v>
+      </c>
+      <c r="E44" s="3">
         <v>2300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4100</v>
-      </c>
-      <c r="F44" s="3">
-        <v>3600</v>
       </c>
       <c r="G44" s="3">
         <v>3600</v>
       </c>
       <c r="H44" s="3">
+        <v>3600</v>
+      </c>
+      <c r="I44" s="3">
         <v>3800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>9200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>14800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>18300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>14900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>28800</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
-      </c>
       <c r="Q44" s="3">
         <v>0</v>
       </c>
@@ -2628,40 +2723,43 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>4</v>
+      <c r="T44" s="3">
+        <v>0</v>
       </c>
       <c r="U44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E45" s="3">
         <v>400</v>
       </c>
       <c r="F45" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G45" s="3">
         <v>200</v>
       </c>
       <c r="H45" s="3">
+        <v>200</v>
+      </c>
+      <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>500</v>
-      </c>
-      <c r="K45" s="3">
-        <v>400</v>
       </c>
       <c r="L45" s="3">
         <v>400</v>
@@ -2670,13 +2768,13 @@
         <v>400</v>
       </c>
       <c r="N45" s="3">
+        <v>400</v>
+      </c>
+      <c r="O45" s="3">
         <v>200</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>4</v>
+      <c r="P45" s="3">
+        <v>0</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>4</v>
@@ -2693,91 +2791,97 @@
       <c r="U45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E46" s="3">
         <v>4000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>17200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>23800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>30100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>23800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>49100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>14700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5200</v>
       </c>
-      <c r="T46" s="3">
-        <v>0</v>
-      </c>
-      <c r="U46" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="U46" s="3">
+        <v>0</v>
+      </c>
+      <c r="V46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E47" s="3">
-        <v>0</v>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F47" s="3">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="G47" s="3">
         <v>1800</v>
       </c>
       <c r="H47" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I47" s="3">
         <v>1500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2200</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
@@ -2793,8 +2897,8 @@
       <c r="O47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -2811,25 +2915,28 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="E48" s="3">
         <v>1000</v>
       </c>
       <c r="F48" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="G48" s="3">
         <v>1100</v>
       </c>
       <c r="H48" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="I48" s="3">
         <v>1200</v>
@@ -2838,10 +2945,10 @@
         <v>1200</v>
       </c>
       <c r="K48" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="L48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3">
         <v>100</v>
@@ -2858,8 +2965,8 @@
       <c r="Q48" s="3">
         <v>100</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>4</v>
+      <c r="R48" s="3">
+        <v>100</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>4</v>
@@ -2870,23 +2977,26 @@
       <c r="U48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E49" s="3">
         <v>11300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11700</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H49" s="3" t="s">
         <v>4</v>
       </c>
@@ -2902,8 +3012,8 @@
       <c r="L49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="M49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -2929,8 +3039,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3101,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,8 +3163,11 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3106,8 +3225,11 @@
       <c r="U52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,67 +3287,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E54" s="3">
         <v>16300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>19400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>21200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>13000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>30200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>23900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>49200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>14700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>9700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5200</v>
       </c>
-      <c r="T54" s="3">
-        <v>0</v>
-      </c>
       <c r="U54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3375,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,82 +3399,86 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E57" s="3">
         <v>1700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2400</v>
       </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
       <c r="J57" s="3">
+        <v>0</v>
+      </c>
+      <c r="K57" s="3">
         <v>900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>12900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>17100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>38300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2400</v>
       </c>
-      <c r="T57" s="3">
-        <v>0</v>
-      </c>
-      <c r="U57" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U57" s="3">
+        <v>0</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="E58" s="3">
         <v>800</v>
       </c>
       <c r="F58" s="3">
+        <v>800</v>
+      </c>
+      <c r="G58" s="3">
         <v>500</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H58" s="3" t="s">
         <v>4</v>
       </c>
@@ -3361,8 +3494,8 @@
       <c r="L58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -3388,8 +3521,11 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3397,117 +3533,123 @@
         <v>1200</v>
       </c>
       <c r="E59" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="F59" s="3">
         <v>1300</v>
       </c>
       <c r="G59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H59" s="3">
         <v>4100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>800</v>
-      </c>
-      <c r="K59" s="3">
-        <v>500</v>
       </c>
       <c r="L59" s="3">
         <v>500</v>
       </c>
       <c r="M59" s="3">
+        <v>500</v>
+      </c>
+      <c r="N59" s="3">
         <v>900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1400</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U59" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E60" s="3">
         <v>3700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>13800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>17500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>39900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2400</v>
       </c>
-      <c r="T60" s="3">
-        <v>0</v>
-      </c>
       <c r="U60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3565,8 +3707,11 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3574,25 +3719,25 @@
         <v>800</v>
       </c>
       <c r="E62" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="F62" s="3">
         <v>900</v>
       </c>
       <c r="G62" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="H62" s="3">
         <v>1000</v>
       </c>
       <c r="I62" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="J62" s="3">
         <v>1100</v>
       </c>
       <c r="K62" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -3604,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="O62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P62" s="3">
         <v>100</v>
@@ -3612,8 +3757,8 @@
       <c r="Q62" s="3">
         <v>100</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>4</v>
+      <c r="R62" s="3">
+        <v>100</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>4</v>
@@ -3624,8 +3769,11 @@
       <c r="U62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3831,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3893,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,67 +3955,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5800</v>
-      </c>
-      <c r="F66" s="3">
-        <v>5200</v>
       </c>
       <c r="G66" s="3">
         <v>5200</v>
       </c>
       <c r="H66" s="3">
+        <v>5200</v>
+      </c>
+      <c r="I66" s="3">
         <v>4800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>17500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>39900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2400</v>
       </c>
-      <c r="T66" s="3">
-        <v>0</v>
-      </c>
       <c r="U66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4043,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4103,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4165,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4060,8 +4227,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,67 +4289,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-34400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-32900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-30800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-28400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-26600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-22600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-19600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-16900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-13100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-8000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-5300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-3600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>4100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2700</v>
-      </c>
-      <c r="T72" s="3">
-        <v>-100</v>
       </c>
       <c r="U72" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4413,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4475,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,67 +4537,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E76" s="3">
         <v>11700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>16300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2800</v>
       </c>
-      <c r="T76" s="3">
-        <v>0</v>
-      </c>
       <c r="U76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4661,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E80" s="2">
         <v>45322</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45230</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45138</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45046</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44957</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44865</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44773</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44681</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44592</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44500</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44408</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44316</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44227</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44135</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44043</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43951</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43861</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43769</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1100</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
       <c r="U81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,8 +4816,9 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4631,16 +4829,16 @@
         <v>200</v>
       </c>
       <c r="F83" s="3">
+        <v>200</v>
+      </c>
+      <c r="G83" s="3">
         <v>100</v>
       </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
       <c r="H83" s="3">
         <v>0</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>4</v>
+      <c r="I83" s="3">
+        <v>0</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>4</v>
@@ -4657,8 +4855,8 @@
       <c r="N83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
+      <c r="O83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
@@ -4678,8 +4876,11 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4938,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5000,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5062,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5124,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,67 +5186,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>500</v>
+      </c>
+      <c r="E89" s="3">
         <v>200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-9300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2000</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
       <c r="U89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,8 +5274,9 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5114,8 +5334,11 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5396,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,8 +5458,11 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5244,16 +5473,16 @@
         <v>0</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-300</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>4</v>
+      <c r="I94" s="3">
+        <v>0</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>4</v>
@@ -5270,8 +5499,8 @@
       <c r="N94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P94" s="3">
         <v>0</v>
@@ -5291,8 +5520,11 @@
       <c r="U94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,8 +5546,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5373,8 +5606,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5668,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5730,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,52 +5792,55 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>500</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>1500</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>9700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>4</v>
+      <c r="Q100" s="3">
+        <v>0</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>4</v>
@@ -5609,8 +5854,11 @@
       <c r="U100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5668,63 +5916,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E102" s="3">
         <v>100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>4800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2000</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
       <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KAVL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KAVL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="92">
   <si>
     <t>KAVL</t>
   </si>
@@ -656,288 +656,301 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E7" s="2">
         <v>45412</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45322</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45230</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45138</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45046</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44957</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44865</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44773</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44681</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44592</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44500</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44408</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44316</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44227</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44135</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44043</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43951</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43861</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43769</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>700</v>
+      </c>
+      <c r="E8" s="3">
         <v>2200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>58800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>18100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>37400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>9400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>32400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>22500</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>300</v>
+      </c>
+      <c r="E9" s="3">
         <v>1700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>46800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>11900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>32600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>28000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>20000</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>400</v>
+      </c>
+      <c r="E10" s="3">
         <v>500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1100</v>
-      </c>
-      <c r="K10" s="3">
-        <v>400</v>
       </c>
       <c r="L10" s="3">
         <v>400</v>
       </c>
       <c r="M10" s="3">
+        <v>400</v>
+      </c>
+      <c r="N10" s="3">
         <v>-700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>12000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>6200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2500</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -960,8 +973,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1022,8 +1036,11 @@
       <c r="V12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,20 +1101,23 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1113,8 +1133,8 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1146,8 +1166,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1157,26 +1180,26 @@
       <c r="E15" s="3">
         <v>200</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>4</v>
+      <c r="F15" s="3">
+        <v>200</v>
+      </c>
+      <c r="G15" s="3">
+        <v>200</v>
+      </c>
+      <c r="H15" s="3">
+        <v>100</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
+      <c r="L15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1208,8 +1231,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E17" s="3">
         <v>3500</v>
       </c>
-      <c r="E17" s="3">
-        <v>5000</v>
-      </c>
       <c r="F17" s="3">
+        <v>4900</v>
+      </c>
+      <c r="G17" s="3">
         <v>6000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>69200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>22200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>36900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>29400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>20400</v>
       </c>
-      <c r="U17" s="3">
-        <v>0</v>
-      </c>
       <c r="V17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1300</v>
       </c>
-      <c r="E18" s="3">
-        <v>-1800</v>
-      </c>
       <c r="F18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="G18" s="3">
         <v>-2000</v>
       </c>
-      <c r="G18" s="3">
-        <v>-1600</v>
-      </c>
       <c r="H18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="I18" s="3">
         <v>-4000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-10400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2100</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,31 +1410,32 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-300</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-400</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1433,38 +1467,41 @@
       <c r="T20" s="3">
         <v>0</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>4</v>
+      <c r="U20" s="3">
+        <v>0</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-1300</v>
+        <v>-1200</v>
       </c>
       <c r="E21" s="3">
-        <v>-1900</v>
+        <v>-1100</v>
       </c>
       <c r="F21" s="3">
-        <v>-2200</v>
+        <v>-1500</v>
       </c>
       <c r="G21" s="3">
-        <v>-1700</v>
+        <v>-1800</v>
       </c>
       <c r="H21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="I21" s="3">
         <v>-4000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-3000</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1477,55 +1514,58 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3">
         <v>-3400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>400</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T21" s="3">
         <v>2900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2100</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1563,78 +1603,84 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-4000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-10500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4100</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>400</v>
       </c>
       <c r="R23" s="3">
         <v>400</v>
       </c>
       <c r="S23" s="3">
+        <v>400</v>
+      </c>
+      <c r="T23" s="3">
         <v>2900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2100</v>
       </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
       <c r="V23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
@@ -1642,14 +1688,14 @@
       <c r="G24" s="3">
         <v>0</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1661,34 +1707,37 @@
         <v>0</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>-1400</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1000</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1100</v>
       </c>
-      <c r="U26" s="3">
-        <v>0</v>
-      </c>
       <c r="V26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1100</v>
       </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
       <c r="V27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1997,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,31 +2188,34 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>200</v>
-      </c>
-      <c r="E32" s="3">
-        <v>300</v>
-      </c>
-      <c r="F32" s="3">
-        <v>400</v>
-      </c>
-      <c r="G32" s="3">
-        <v>200</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2177,14 +2247,17 @@
       <c r="T32" s="3">
         <v>0</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>4</v>
+      <c r="U32" s="3">
+        <v>0</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2192,61 +2265,64 @@
         <v>-1600</v>
       </c>
       <c r="E33" s="3">
-        <v>-2200</v>
+        <v>-1500</v>
       </c>
       <c r="F33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="G33" s="3">
         <v>-2400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1100</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
       <c r="V33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,8 +2383,11 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2316,128 +2395,134 @@
         <v>-1600</v>
       </c>
       <c r="E35" s="3">
-        <v>-2200</v>
+        <v>-1500</v>
       </c>
       <c r="F35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="G35" s="3">
         <v>-2400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1100</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
       <c r="V35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E38" s="2">
         <v>45412</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45322</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45230</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45138</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45046</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44957</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44865</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44773</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44681</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44592</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44500</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44408</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44316</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44227</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44135</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44043</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43951</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43861</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43769</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,70 +2570,74 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E41" s="3">
         <v>500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2000</v>
       </c>
-      <c r="U41" s="3">
-        <v>0</v>
-      </c>
-      <c r="V41" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="V41" s="3">
+        <v>0</v>
+      </c>
+      <c r="W41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2608,115 +2698,121 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="E43" s="3">
         <v>700</v>
       </c>
       <c r="F43" s="3">
+        <v>700</v>
+      </c>
+      <c r="G43" s="3">
         <v>1900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>18100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>12700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3200</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>200</v>
+      </c>
+      <c r="E44" s="3">
         <v>600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4100</v>
-      </c>
-      <c r="G44" s="3">
-        <v>3600</v>
       </c>
       <c r="H44" s="3">
         <v>3600</v>
       </c>
       <c r="I44" s="3">
+        <v>3600</v>
+      </c>
+      <c r="J44" s="3">
         <v>3800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>9200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>14800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>18300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>14900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>28800</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
       <c r="R44" s="3">
         <v>0</v>
       </c>
@@ -2726,43 +2822,46 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>4</v>
+      <c r="U44" s="3">
+        <v>0</v>
       </c>
       <c r="V44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>200</v>
-      </c>
-      <c r="E45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
         <v>400</v>
       </c>
-      <c r="F45" s="3">
-        <v>400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>200</v>
-      </c>
-      <c r="H45" s="3">
-        <v>200</v>
-      </c>
-      <c r="I45" s="3">
-        <v>300</v>
-      </c>
-      <c r="J45" s="3">
-        <v>400</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>500</v>
-      </c>
-      <c r="L45" s="3">
-        <v>400</v>
       </c>
       <c r="M45" s="3">
         <v>400</v>
@@ -2771,13 +2870,13 @@
         <v>400</v>
       </c>
       <c r="O45" s="3">
+        <v>400</v>
+      </c>
+      <c r="P45" s="3">
         <v>200</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="3" t="s">
-        <v>4</v>
+      <c r="Q45" s="3">
+        <v>0</v>
       </c>
       <c r="R45" s="3" t="s">
         <v>4</v>
@@ -2794,70 +2893,76 @@
       <c r="V45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E46" s="3">
         <v>1900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>17200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>23800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>30100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>23800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>49100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>14700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5200</v>
       </c>
-      <c r="U46" s="3">
-        <v>0</v>
-      </c>
-      <c r="V46" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="V46" s="3">
+        <v>0</v>
+      </c>
+      <c r="W46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2867,24 +2972,24 @@
       <c r="E47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>1800</v>
-      </c>
-      <c r="H47" s="3">
-        <v>1800</v>
-      </c>
-      <c r="I47" s="3">
-        <v>1500</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K47" s="3">
         <v>2200</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
@@ -2900,8 +3005,8 @@
       <c r="P47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -2918,8 +3023,11 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2927,19 +3035,19 @@
         <v>900</v>
       </c>
       <c r="E48" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="F48" s="3">
         <v>1000</v>
       </c>
       <c r="G48" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="H48" s="3">
         <v>1100</v>
       </c>
       <c r="I48" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="J48" s="3">
         <v>1200</v>
@@ -2948,10 +3056,10 @@
         <v>1200</v>
       </c>
       <c r="L48" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="M48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3">
         <v>100</v>
@@ -2968,8 +3076,8 @@
       <c r="R48" s="3">
         <v>100</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>4</v>
+      <c r="S48" s="3">
+        <v>100</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>4</v>
@@ -2980,31 +3088,34 @@
       <c r="V48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E49" s="3">
         <v>11100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11700</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>4</v>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>4</v>
@@ -3015,8 +3126,8 @@
       <c r="M49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="N49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -3042,8 +3153,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,31 +3283,34 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -3228,8 +3348,11 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,70 +3413,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E54" s="3">
         <v>13900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>16300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>19400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>21200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>13000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>17300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>23800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>30200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>23900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>49200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>14700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>9700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5200</v>
       </c>
-      <c r="U54" s="3">
-        <v>0</v>
-      </c>
       <c r="V54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,93 +3530,97 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E57" s="3">
         <v>1800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2400</v>
       </c>
-      <c r="H57" s="3">
-        <v>200</v>
-      </c>
       <c r="I57" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J57" s="3">
         <v>2400</v>
       </c>
-      <c r="J57" s="3">
-        <v>0</v>
-      </c>
       <c r="K57" s="3">
+        <v>0</v>
+      </c>
+      <c r="L57" s="3">
         <v>900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>12900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>17100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>38300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2400</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
-      </c>
-      <c r="V57" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V57" s="3">
+        <v>0</v>
+      </c>
+      <c r="W57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="E58" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="F58" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="G58" s="3">
-        <v>500</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>4</v>
+        <v>1000</v>
+      </c>
+      <c r="H58" s="3">
+        <v>700</v>
+      </c>
+      <c r="I58" s="3">
+        <v>200</v>
+      </c>
+      <c r="J58" s="3">
+        <v>200</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>4</v>
@@ -3497,8 +3631,8 @@
       <c r="M58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -3524,70 +3658,76 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="E59" s="3">
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="F59" s="3">
-        <v>1300</v>
+        <v>300</v>
       </c>
       <c r="G59" s="3">
-        <v>1300</v>
+        <v>400</v>
       </c>
       <c r="H59" s="3">
-        <v>4100</v>
+        <v>600</v>
       </c>
       <c r="I59" s="3">
-        <v>1400</v>
+        <v>1100</v>
       </c>
       <c r="J59" s="3">
+        <v>500</v>
+      </c>
+      <c r="K59" s="3">
         <v>1500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>800</v>
-      </c>
-      <c r="L59" s="3">
-        <v>500</v>
       </c>
       <c r="M59" s="3">
         <v>500</v>
       </c>
       <c r="N59" s="3">
+        <v>500</v>
+      </c>
+      <c r="O59" s="3">
         <v>900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1400</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V59" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3595,84 +3735,87 @@
         <v>3300</v>
       </c>
       <c r="E60" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F60" s="3">
         <v>3700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>13800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>17500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>39900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2400</v>
       </c>
-      <c r="U60" s="3">
-        <v>0</v>
-      </c>
       <c r="V60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3710,37 +3853,40 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>800</v>
-      </c>
-      <c r="E62" s="3">
-        <v>800</v>
-      </c>
-      <c r="F62" s="3">
-        <v>900</v>
-      </c>
-      <c r="G62" s="3">
-        <v>900</v>
-      </c>
-      <c r="H62" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I62" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J62" s="3">
-        <v>1100</v>
+      <c r="D62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K62" s="3">
         <v>1100</v>
       </c>
       <c r="L62" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -3752,7 +3898,7 @@
         <v>0</v>
       </c>
       <c r="P62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q62" s="3">
         <v>100</v>
@@ -3760,8 +3906,8 @@
       <c r="R62" s="3">
         <v>100</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>4</v>
+      <c r="S62" s="3">
+        <v>100</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>4</v>
@@ -3772,8 +3918,11 @@
       <c r="V62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,8 +4113,11 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -3967,61 +4125,64 @@
         <v>4000</v>
       </c>
       <c r="E66" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F66" s="3">
         <v>4500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5800</v>
-      </c>
-      <c r="G66" s="3">
-        <v>5200</v>
       </c>
       <c r="H66" s="3">
         <v>5200</v>
       </c>
       <c r="I66" s="3">
+        <v>5200</v>
+      </c>
+      <c r="J66" s="3">
         <v>4800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>17500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>39900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>8900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2400</v>
       </c>
-      <c r="U66" s="3">
-        <v>0</v>
-      </c>
       <c r="V66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4230,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,70 +4463,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-34400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-32900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-30800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-28400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-26600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-22600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-19600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-16900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-13100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-8000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-5300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-3600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>4100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2700</v>
-      </c>
-      <c r="U72" s="3">
-        <v>-100</v>
       </c>
       <c r="V72" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,70 +4723,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E76" s="3">
         <v>9900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>16300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2800</v>
       </c>
-      <c r="U76" s="3">
-        <v>0</v>
-      </c>
       <c r="V76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,75 +4853,81 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E80" s="2">
         <v>45412</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45322</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45230</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45138</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45046</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44957</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44865</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44773</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44681</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44592</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44500</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44408</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44316</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44227</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44135</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44043</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43951</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43861</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43769</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4740,61 +4935,64 @@
         <v>-1600</v>
       </c>
       <c r="E81" s="3">
-        <v>-2200</v>
+        <v>-1500</v>
       </c>
       <c r="F81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="G81" s="3">
         <v>-2400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1100</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
       <c r="V81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,28 +5015,29 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F83" s="3">
-        <v>200</v>
-      </c>
-      <c r="G83" s="3">
-        <v>100</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>4</v>
@@ -4858,8 +5057,8 @@
       <c r="O83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="P83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -4879,8 +5078,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,70 +5403,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E89" s="3">
         <v>500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-9300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-5400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2000</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
       <c r="V89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,19 +5495,20 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -5337,8 +5558,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,31 +5688,34 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-300</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
         <v>0</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>4</v>
+      <c r="J94" s="3">
+        <v>0</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>4</v>
@@ -5502,8 +5732,8 @@
       <c r="O94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
+      <c r="P94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q94" s="3">
         <v>0</v>
@@ -5523,8 +5753,11 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,31 +5780,32 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5609,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,55 +6038,58 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>500</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>1500</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>9700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>4</v>
+      <c r="R100" s="3">
+        <v>0</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>4</v>
@@ -5857,31 +6103,34 @@
       <c r="V100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5919,66 +6168,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-5500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2000</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
       <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KAVL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KAVL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
   <si>
     <t>KAVL</t>
   </si>
@@ -656,301 +656,327 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F7" s="2">
         <v>45504</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45412</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45322</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45230</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45138</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45046</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44957</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44865</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44773</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44681</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44592</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44500</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44408</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44316</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44227</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44135</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44043</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43951</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43861</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43769</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>200</v>
+      </c>
+      <c r="E8" s="3">
         <v>700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
+        <v>700</v>
+      </c>
+      <c r="G8" s="3">
         <v>2200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>3200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>4000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>3600</v>
-      </c>
-      <c r="I8" s="3">
-        <v>3000</v>
-      </c>
-      <c r="J8" s="3">
-        <v>2500</v>
       </c>
       <c r="K8" s="3">
         <v>3000</v>
       </c>
       <c r="L8" s="3">
+        <v>2500</v>
+      </c>
+      <c r="M8" s="3">
+        <v>3000</v>
+      </c>
+      <c r="N8" s="3">
         <v>3800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>3100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>2800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>58800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>3400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>18100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>37400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>9400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>32400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>22500</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W8" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="3">
+        <v>200</v>
+      </c>
+      <c r="F9" s="3">
         <v>300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>2000</v>
-      </c>
-      <c r="G9" s="3">
-        <v>3100</v>
-      </c>
-      <c r="H9" s="3">
-        <v>2300</v>
       </c>
       <c r="I9" s="3">
         <v>3100</v>
       </c>
       <c r="J9" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K9" s="3">
+        <v>3100</v>
+      </c>
+      <c r="L9" s="3">
         <v>2000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>3400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>2700</v>
-      </c>
-      <c r="N9" s="3">
-        <v>3500</v>
-      </c>
-      <c r="O9" s="3">
-        <v>46800</v>
       </c>
       <c r="P9" s="3">
         <v>3500</v>
       </c>
       <c r="Q9" s="3">
+        <v>46800</v>
+      </c>
+      <c r="R9" s="3">
+        <v>3500</v>
+      </c>
+      <c r="S9" s="3">
         <v>11900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>32600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>6300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>28000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>20000</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W9" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E10" s="3">
         <v>500</v>
       </c>
       <c r="F10" s="3">
+        <v>400</v>
+      </c>
+      <c r="G10" s="3">
+        <v>500</v>
+      </c>
+      <c r="H10" s="3">
         <v>1200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>1300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>-700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>12000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>-100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>6200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>4800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>3100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>4400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>2500</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W10" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -974,8 +1000,10 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1039,8 +1067,14 @@
       <c r="W12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,25 +1138,31 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="E14" s="3">
         <v>100</v>
       </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
+      <c r="H14" s="3">
+        <v>100</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>4</v>
@@ -1136,11 +1176,11 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1169,8 +1209,14 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1187,25 +1233,25 @@
         <v>200</v>
       </c>
       <c r="H15" s="3">
+        <v>200</v>
+      </c>
+      <c r="I15" s="3">
+        <v>200</v>
+      </c>
+      <c r="J15" s="3">
         <v>100</v>
       </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1234,8 +1280,14 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1308,152 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E17" s="3">
         <v>2100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G17" s="3">
         <v>3500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>4900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>6000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>5200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>7000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>5500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>5700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>7700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>8100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>5600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>69200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>6900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>22200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>36900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>9100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>29400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>20400</v>
       </c>
-      <c r="V17" s="3">
-        <v>0</v>
-      </c>
-      <c r="W17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-1400</v>
+        <v>-4100</v>
       </c>
       <c r="E18" s="3">
         <v>-1300</v>
       </c>
       <c r="F18" s="3">
-        <v>-1700</v>
+        <v>-1400</v>
       </c>
       <c r="G18" s="3">
-        <v>-2000</v>
+        <v>-1300</v>
       </c>
       <c r="H18" s="3">
         <v>-1700</v>
       </c>
       <c r="I18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="K18" s="3">
         <v>-4000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-3000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-2700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-3900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-5000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-2800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-10400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-4100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>3000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>2100</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W18" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,8 +1477,10 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1437,11 +1505,11 @@
       <c r="J20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1470,44 +1538,50 @@
       <c r="U20" s="3">
         <v>0</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W20" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-1200</v>
+        <v>-3900</v>
       </c>
       <c r="E21" s="3">
         <v>-1100</v>
       </c>
       <c r="F21" s="3">
-        <v>-1500</v>
+        <v>-1200</v>
       </c>
       <c r="G21" s="3">
-        <v>-1800</v>
+        <v>-1100</v>
       </c>
       <c r="H21" s="3">
         <v>-1500</v>
       </c>
       <c r="I21" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="K21" s="3">
         <v>-4000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-3000</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1517,61 +1591,67 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-4100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>400</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V21" s="3">
         <v>2900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>2100</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W21" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
         <v>200</v>
-      </c>
-      <c r="E22" s="3">
-        <v>300</v>
-      </c>
-      <c r="F22" s="3">
-        <v>300</v>
       </c>
       <c r="G22" s="3">
         <v>300</v>
       </c>
       <c r="H22" s="3">
+        <v>300</v>
+      </c>
+      <c r="I22" s="3">
+        <v>300</v>
+      </c>
+      <c r="J22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1606,102 +1686,114 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-1600</v>
+        <v>-4100</v>
       </c>
       <c r="E23" s="3">
         <v>-1500</v>
       </c>
       <c r="F23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="H23" s="3">
         <v>-2100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-2400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-1800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-4000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-3000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-2700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-3900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-5000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-2800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-10500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-4100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>2900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>2100</v>
       </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
-      <c r="W23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>4</v>
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1710,34 +1802,40 @@
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>-1400</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>200</v>
-      </c>
       <c r="R24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S24" s="3">
         <v>200</v>
       </c>
       <c r="T24" s="3">
+        <v>100</v>
+      </c>
+      <c r="U24" s="3">
+        <v>200</v>
+      </c>
+      <c r="V24" s="3">
         <v>300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>1000</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W24" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1899,156 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-1600</v>
+        <v>-4100</v>
       </c>
       <c r="E26" s="3">
         <v>-1500</v>
       </c>
       <c r="F26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="H26" s="3">
         <v>-2100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-2400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-1800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-4000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-3000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-2700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-3900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-5000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-2800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-9000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-4300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>2600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>1100</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
-      <c r="W26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-2200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-2400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-1800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-4000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-3000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-2700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-3900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-5000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-2800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-9000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-4300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>2600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>1100</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
-      <c r="W27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2112,14 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2061,8 +2183,14 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2254,14 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,8 +2325,14 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2217,11 +2357,11 @@
       <c r="J32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -2250,79 +2390,91 @@
       <c r="U32" s="3">
         <v>0</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W32" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-1600</v>
+        <v>-4100</v>
       </c>
       <c r="E33" s="3">
         <v>-1500</v>
       </c>
       <c r="F33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="H33" s="3">
         <v>-2100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-2400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-1800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-4000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-3000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-2700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-3900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-5000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-2800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-9000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-4300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>2600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>1100</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
-      <c r="W33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2538,161 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-1600</v>
+        <v>-4100</v>
       </c>
       <c r="E35" s="3">
         <v>-1500</v>
       </c>
       <c r="F35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="H35" s="3">
         <v>-2100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-2400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-1800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-4000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-3000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-2700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-3900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-5000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-2800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-9000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-4300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>2600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>1100</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
-      <c r="W35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F38" s="2">
         <v>45504</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45412</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45322</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45230</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45138</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45046</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44957</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44865</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44773</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44681</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44592</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44500</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44408</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44316</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44227</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44135</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44043</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43951</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43861</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43769</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2716,10 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,73 +2743,81 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F41" s="3">
         <v>4500</v>
-      </c>
-      <c r="E41" s="3">
-        <v>500</v>
-      </c>
-      <c r="F41" s="3">
-        <v>600</v>
       </c>
       <c r="G41" s="3">
         <v>500</v>
       </c>
       <c r="H41" s="3">
+        <v>600</v>
+      </c>
+      <c r="I41" s="3">
+        <v>500</v>
+      </c>
+      <c r="J41" s="3">
         <v>1000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>3800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>3700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>3400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>4700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>5600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>7800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>2100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>2000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>7400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>2700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>2000</v>
       </c>
-      <c r="V41" s="3">
-        <v>0</v>
-      </c>
-      <c r="W41" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2701,138 +2881,156 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>300</v>
+      </c>
+      <c r="F43" s="3">
         <v>500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>3000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>3700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>3200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>2900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>3000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>3700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>7700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>18100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>12700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>7100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>3200</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W43" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3">
         <v>200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>2300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>4100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>3600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>3600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>3800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>5800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>9200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>14800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>18300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>14900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>28800</v>
       </c>
-      <c r="R44" s="3">
-        <v>0</v>
-      </c>
-      <c r="S44" s="3">
-        <v>0</v>
-      </c>
       <c r="T44" s="3">
         <v>0</v>
       </c>
       <c r="U44" s="3">
         <v>0</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W44" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+      <c r="X44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2857,32 +3055,32 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
-        <v>400</v>
-      </c>
-      <c r="L45" s="3">
-        <v>500</v>
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M45" s="3">
         <v>400</v>
       </c>
       <c r="N45" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="O45" s="3">
         <v>400</v>
       </c>
       <c r="P45" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>400</v>
+      </c>
+      <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S45" s="3" t="s">
-        <v>4</v>
+      <c r="S45" s="3">
+        <v>0</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>4</v>
@@ -2896,73 +3094,85 @@
       <c r="W45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F46" s="3">
         <v>5800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>4000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>6900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>6600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>7900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>10400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>9100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>12900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>17200</v>
-      </c>
-      <c r="N46" s="3">
-        <v>23800</v>
-      </c>
-      <c r="O46" s="3">
-        <v>30100</v>
       </c>
       <c r="P46" s="3">
         <v>23800</v>
       </c>
       <c r="Q46" s="3">
+        <v>30100</v>
+      </c>
+      <c r="R46" s="3">
+        <v>23800</v>
+      </c>
+      <c r="S46" s="3">
         <v>49100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>14700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>8800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>9700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>5200</v>
       </c>
-      <c r="V46" s="3">
-        <v>0</v>
-      </c>
-      <c r="W46" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2987,15 +3197,15 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M47" s="3">
         <v>2200</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>4</v>
       </c>
@@ -3008,11 +3218,11 @@
       <c r="Q47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
-      </c>
-      <c r="S47" s="3">
-        <v>0</v>
+      <c r="R47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T47" s="3">
         <v>0</v>
@@ -3026,46 +3236,52 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>800</v>
+      </c>
+      <c r="F48" s="3">
         <v>900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1100</v>
-      </c>
-      <c r="J48" s="3">
-        <v>1200</v>
-      </c>
-      <c r="K48" s="3">
-        <v>1200</v>
       </c>
       <c r="L48" s="3">
         <v>1200</v>
       </c>
       <c r="M48" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="N48" s="3">
-        <v>100</v>
+        <v>1200</v>
       </c>
       <c r="O48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3">
         <v>100</v>
@@ -3079,11 +3295,11 @@
       <c r="S48" s="3">
         <v>100</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U48" s="3" t="s">
-        <v>4</v>
+      <c r="T48" s="3">
+        <v>100</v>
+      </c>
+      <c r="U48" s="3">
+        <v>100</v>
       </c>
       <c r="V48" s="3" t="s">
         <v>4</v>
@@ -3091,37 +3307,43 @@
       <c r="W48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E49" s="3">
+        <v>10700</v>
+      </c>
+      <c r="F49" s="3">
         <v>10900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>11100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>11300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>11500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>11700</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>4</v>
+      <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>4</v>
@@ -3129,11 +3351,11 @@
       <c r="N49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
-      <c r="P49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
@@ -3156,8 +3378,14 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3449,14 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,8 +3520,14 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3303,21 +3543,21 @@
       <c r="G52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3">
         <v>1800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1500</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
@@ -3351,8 +3591,14 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,73 +3662,85 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>16000</v>
+      </c>
+      <c r="F54" s="3">
         <v>17500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>13900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>16300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>19400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>21200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>10800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>13000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>12400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>14100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>17300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>23800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>30200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>23900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>49200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>14700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>8900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>9700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>5200</v>
       </c>
-      <c r="V54" s="3">
-        <v>0</v>
-      </c>
-      <c r="W54" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3764,10 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,114 +3791,122 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>200</v>
+      </c>
+      <c r="F57" s="3">
         <v>1600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2800</v>
-      </c>
-      <c r="H57" s="3">
-        <v>2400</v>
-      </c>
-      <c r="I57" s="3">
-        <v>2300</v>
       </c>
       <c r="J57" s="3">
         <v>2400</v>
       </c>
       <c r="K57" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="L57" s="3">
+        <v>2400</v>
+      </c>
+      <c r="M57" s="3">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3">
         <v>900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>3600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>9300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>12900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>17100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>38300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>6200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>4300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>2400</v>
       </c>
-      <c r="V57" s="3">
-        <v>0</v>
-      </c>
-      <c r="W57" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>400</v>
+      </c>
+      <c r="F58" s="3">
         <v>600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>200</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -3661,168 +3929,186 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3">
         <v>500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>2600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>3000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1400</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W59" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F60" s="3">
         <v>3300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>3700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>5000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>4300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>4200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>3800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>4100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>9800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>13800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>17500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>39900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>8900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>4400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>5700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>2400</v>
       </c>
-      <c r="V60" s="3">
-        <v>0</v>
-      </c>
-      <c r="W60" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>600</v>
+      </c>
+      <c r="E61" s="3">
         <v>700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
+        <v>700</v>
+      </c>
+      <c r="G61" s="3">
         <v>800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1000</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3856,8 +4142,14 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3882,18 +4174,18 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3">
         <v>1100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1100</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
       <c r="O62" s="3">
         <v>0</v>
       </c>
@@ -3901,19 +4193,19 @@
         <v>0</v>
       </c>
       <c r="Q62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S62" s="3">
         <v>100</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U62" s="3" t="s">
-        <v>4</v>
+      <c r="T62" s="3">
+        <v>100</v>
+      </c>
+      <c r="U62" s="3">
+        <v>100</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>4</v>
@@ -3921,8 +4213,14 @@
       <c r="W62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4284,14 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4355,14 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,73 +4426,85 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F66" s="3">
         <v>4000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>4500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>5800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>5200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>5200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>4800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>2900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>4100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>9900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>13900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>17500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>39900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>8900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>4500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>5700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>2400</v>
       </c>
-      <c r="V66" s="3">
-        <v>0</v>
-      </c>
-      <c r="W66" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4528,10 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4595,14 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4666,14 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4401,8 +4737,14 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,73 +4808,85 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-41500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-37500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-36000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-34400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-32900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-30800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-28400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-26600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-22600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-19600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-16900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-13100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-8000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-5300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>4100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>3800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>3600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>2700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4950,14 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +5021,14 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,73 +5092,85 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>13800</v>
+      </c>
+      <c r="F76" s="3">
         <v>13500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>9900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>11700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>13600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>16000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>5600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>8200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>9800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>11200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>13100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>13900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>16300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>6400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>9200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>5800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>4400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>4000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>2800</v>
       </c>
-      <c r="V76" s="3">
-        <v>0</v>
-      </c>
-      <c r="W76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5234,161 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F80" s="2">
         <v>45504</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45412</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45322</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45230</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45138</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45046</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44957</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44865</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44773</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44681</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44592</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44500</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44408</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44316</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44227</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44135</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44043</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43951</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43861</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43769</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-1600</v>
+        <v>-4100</v>
       </c>
       <c r="E81" s="3">
         <v>-1500</v>
       </c>
       <c r="F81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="H81" s="3">
         <v>-2100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-2400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-1800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-4000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-3000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-2700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-3900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-5000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-2800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-9000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-4300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>2600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>1100</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
-      <c r="W81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,25 +5412,27 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>200</v>
+      </c>
+      <c r="E83" s="3">
+        <v>200</v>
+      </c>
+      <c r="F83" s="3">
         <v>100</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>4</v>
+      <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>4</v>
@@ -5060,11 +5458,11 @@
       <c r="P83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
@@ -5081,8 +5479,14 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5550,14 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5621,14 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5692,14 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5763,14 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,73 +5834,85 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F89" s="3">
         <v>-600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-2600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-2500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-2100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-9300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-5400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>4900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>2000</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,8 +5936,10 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5510,11 +5952,11 @@
       <c r="F91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
@@ -5561,8 +6003,14 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +6074,14 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,8 +6145,14 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5705,23 +6165,23 @@
       <c r="F94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-300</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>4</v>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>4</v>
@@ -5735,11 +6195,11 @@
       <c r="P94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S94" s="3">
         <v>0</v>
@@ -5756,8 +6216,14 @@
       <c r="W94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,8 +6247,10 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5807,11 +6275,11 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5846,8 +6314,14 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6385,14 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6456,14 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,61 +6527,67 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>200</v>
+      </c>
+      <c r="F100" s="3">
         <v>4600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>500</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>1500</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>9700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-100</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>4</v>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>4</v>
@@ -6106,8 +6598,14 @@
       <c r="W100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6132,11 +6630,11 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6171,69 +6669,81 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F102" s="3">
         <v>4000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-2600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-1400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-2200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-5500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>4800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>2000</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KAVL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KAVL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="92">
   <si>
     <t>KAVL</t>
   </si>
@@ -656,327 +656,339 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E7" s="2">
         <v>45688</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45596</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45504</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45412</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45322</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45230</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45138</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45046</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44957</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44865</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44773</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44681</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44592</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44500</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44408</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44316</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44227</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44135</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44043</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43951</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43861</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43769</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3">
         <v>200</v>
-      </c>
-      <c r="E8" s="3">
-        <v>700</v>
       </c>
       <c r="F8" s="3">
         <v>700</v>
       </c>
       <c r="G8" s="3">
+        <v>700</v>
+      </c>
+      <c r="H8" s="3">
         <v>2200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>58800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>18100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>37400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>9400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>32400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>22500</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="3">
         <v>200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>46800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>11900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>32600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>6300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>28000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>20000</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
         <v>200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1100</v>
-      </c>
-      <c r="N10" s="3">
-        <v>400</v>
       </c>
       <c r="O10" s="3">
         <v>400</v>
       </c>
       <c r="P10" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q10" s="3">
         <v>-700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>12000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>6200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>4400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2500</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,8 +1014,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1073,8 +1086,11 @@
       <c r="Y12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,29 +1160,32 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1182,8 +1201,8 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1215,8 +1234,11 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1239,22 +1261,22 @@
         <v>200</v>
       </c>
       <c r="J15" s="3">
+        <v>200</v>
+      </c>
+      <c r="K15" s="3">
         <v>100</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>4</v>
+      <c r="M15" s="3">
+        <v>0</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1286,8 +1308,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1335,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4300</v>
-      </c>
-      <c r="E17" s="3">
-        <v>2100</v>
       </c>
       <c r="F17" s="3">
         <v>2100</v>
       </c>
       <c r="G17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H17" s="3">
         <v>3500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>69200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>22200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>36900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>29400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>20400</v>
       </c>
-      <c r="X17" s="3">
-        <v>0</v>
-      </c>
       <c r="Y17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-10400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-4100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2100</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,8 +1511,9 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1511,8 +1544,8 @@
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1544,47 +1577,50 @@
       <c r="W20" s="3">
         <v>0</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>4</v>
+      <c r="X20" s="3">
+        <v>0</v>
       </c>
       <c r="Y20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-4000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-3000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1597,32 +1633,35 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3">
         <v>-3400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-4100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>400</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W21" s="3">
         <v>2900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2100</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1633,10 +1672,10 @@
         <v>0</v>
       </c>
       <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
         <v>200</v>
-      </c>
-      <c r="G22" s="3">
-        <v>300</v>
       </c>
       <c r="H22" s="3">
         <v>300</v>
@@ -1645,16 +1684,16 @@
         <v>300</v>
       </c>
       <c r="J22" s="3">
+        <v>300</v>
+      </c>
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1692,102 +1731,108 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-10500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4100</v>
-      </c>
-      <c r="T23" s="3">
-        <v>400</v>
       </c>
       <c r="U23" s="3">
         <v>400</v>
       </c>
       <c r="V23" s="3">
+        <v>400</v>
+      </c>
+      <c r="W23" s="3">
         <v>2900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2100</v>
       </c>
-      <c r="X23" s="3">
-        <v>0</v>
-      </c>
       <c r="Y23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>4</v>
+      <c r="F24" s="3">
+        <v>0</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>4</v>
+      <c r="J24" s="3">
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>4</v>
@@ -1795,8 +1840,8 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1808,34 +1853,37 @@
         <v>0</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>-1400</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1000</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1953,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-9000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1100</v>
       </c>
-      <c r="X26" s="3">
-        <v>0</v>
-      </c>
       <c r="Y26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-9000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1100</v>
       </c>
-      <c r="X27" s="3">
-        <v>0</v>
-      </c>
       <c r="Y27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2175,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,8 +2249,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2323,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,8 +2397,11 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2363,8 +2432,8 @@
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -2396,85 +2465,91 @@
       <c r="W32" s="3">
         <v>0</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>4</v>
+      <c r="X32" s="3">
+        <v>0</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-9000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1100</v>
       </c>
-      <c r="X33" s="3">
-        <v>0</v>
-      </c>
       <c r="Y33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2619,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-9000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1100</v>
       </c>
-      <c r="X35" s="3">
-        <v>0</v>
-      </c>
       <c r="Y35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E38" s="2">
         <v>45688</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45596</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45504</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45412</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45322</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45230</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45138</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45046</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44957</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44865</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44773</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44681</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44592</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44500</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44408</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44316</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44227</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44135</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44043</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43951</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43861</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43769</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2802,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,79 +2830,83 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E41" s="3">
         <v>2400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2000</v>
       </c>
-      <c r="X41" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y41" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2887,79 +2976,85 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>100</v>
+      </c>
+      <c r="E43" s="3">
         <v>200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>500</v>
-      </c>
-      <c r="G43" s="3">
-        <v>700</v>
       </c>
       <c r="H43" s="3">
         <v>700</v>
       </c>
       <c r="I43" s="3">
+        <v>700</v>
+      </c>
+      <c r="J43" s="3">
         <v>1900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>18100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>12700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>7100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3200</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2969,51 +3064,51 @@
       <c r="E44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3">
         <v>200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4100</v>
-      </c>
-      <c r="J44" s="3">
-        <v>3600</v>
       </c>
       <c r="K44" s="3">
         <v>3600</v>
       </c>
       <c r="L44" s="3">
+        <v>3600</v>
+      </c>
+      <c r="M44" s="3">
         <v>3800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>9200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>14800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>18300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>14900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>28800</v>
       </c>
-      <c r="T44" s="3">
-        <v>0</v>
-      </c>
       <c r="U44" s="3">
         <v>0</v>
       </c>
@@ -3023,14 +3118,17 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>4</v>
+      <c r="X44" s="3">
+        <v>0</v>
       </c>
       <c r="Y44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3061,14 +3159,14 @@
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>500</v>
-      </c>
-      <c r="O45" s="3">
-        <v>400</v>
       </c>
       <c r="P45" s="3">
         <v>400</v>
@@ -3077,13 +3175,13 @@
         <v>400</v>
       </c>
       <c r="R45" s="3">
+        <v>400</v>
+      </c>
+      <c r="S45" s="3">
         <v>200</v>
       </c>
-      <c r="S45" s="3">
-        <v>0</v>
-      </c>
-      <c r="T45" s="3" t="s">
-        <v>4</v>
+      <c r="T45" s="3">
+        <v>0</v>
       </c>
       <c r="U45" s="3" t="s">
         <v>4</v>
@@ -3100,79 +3198,85 @@
       <c r="Y45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E46" s="3">
         <v>2800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>17200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>23800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>30100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>23800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>49100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>14700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>8800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>9700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5200</v>
       </c>
-      <c r="X46" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y46" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3203,12 +3307,12 @@
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N47" s="3">
         <v>2200</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>4</v>
       </c>
@@ -3224,8 +3328,8 @@
       <c r="S47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T47" s="3">
-        <v>0</v>
+      <c r="T47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U47" s="3">
         <v>0</v>
@@ -3242,37 +3346,40 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>800</v>
+      <c r="D48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E48" s="3">
         <v>800</v>
       </c>
       <c r="F48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="G48" s="3">
         <v>900</v>
       </c>
       <c r="H48" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="I48" s="3">
         <v>1000</v>
       </c>
       <c r="J48" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="K48" s="3">
         <v>1100</v>
       </c>
       <c r="L48" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="M48" s="3">
         <v>1200</v>
@@ -3281,10 +3388,10 @@
         <v>1200</v>
       </c>
       <c r="O48" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="P48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3">
         <v>100</v>
@@ -3301,8 +3408,8 @@
       <c r="U48" s="3">
         <v>100</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>4</v>
+      <c r="V48" s="3">
+        <v>100</v>
       </c>
       <c r="W48" s="3" t="s">
         <v>4</v>
@@ -3313,40 +3420,43 @@
       <c r="Y48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E49" s="3">
         <v>10500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11700</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>4</v>
+      <c r="M49" s="3">
+        <v>0</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>4</v>
@@ -3357,8 +3467,8 @@
       <c r="P49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
@@ -3384,8 +3494,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3568,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,8 +3642,11 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3549,18 +3668,18 @@
       <c r="I52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J52" s="3">
-        <v>1800</v>
+      <c r="J52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K52" s="3">
         <v>1800</v>
       </c>
       <c r="L52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M52" s="3">
         <v>1500</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
       <c r="N52" s="3">
         <v>0</v>
       </c>
@@ -3597,8 +3716,11 @@
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,79 +3790,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E54" s="3">
         <v>14100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>16000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>17500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>13900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>16300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>19400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>21200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>13000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>12400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>17300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>23800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>30200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>23900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>49200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>14700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>8900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>9700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5200</v>
       </c>
-      <c r="X54" s="3">
-        <v>0</v>
-      </c>
       <c r="Y54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3894,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,8 +3922,9 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3802,102 +3932,105 @@
         <v>100</v>
       </c>
       <c r="E57" s="3">
+        <v>100</v>
+      </c>
+      <c r="F57" s="3">
         <v>200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2400</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
       <c r="N57" s="3">
+        <v>0</v>
+      </c>
+      <c r="O57" s="3">
         <v>900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>12900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>17100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>38300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2400</v>
       </c>
-      <c r="X57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y57" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>200</v>
+      </c>
+      <c r="E58" s="3">
         <v>300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>500</v>
-      </c>
-      <c r="H58" s="3">
-        <v>1000</v>
       </c>
       <c r="I58" s="3">
         <v>1000</v>
       </c>
       <c r="J58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K58" s="3">
         <v>700</v>
-      </c>
-      <c r="K58" s="3">
-        <v>200</v>
       </c>
       <c r="L58" s="3">
         <v>200</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>4</v>
+      <c r="M58" s="3">
+        <v>200</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>4</v>
@@ -3908,8 +4041,8 @@
       <c r="P58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -3935,8 +4068,11 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3946,139 +4082,145 @@
       <c r="E59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G59" s="3">
         <v>500</v>
-      </c>
-      <c r="G59" s="3">
-        <v>300</v>
       </c>
       <c r="H59" s="3">
         <v>300</v>
       </c>
       <c r="I59" s="3">
+        <v>300</v>
+      </c>
+      <c r="J59" s="3">
         <v>400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>800</v>
-      </c>
-      <c r="O59" s="3">
-        <v>500</v>
       </c>
       <c r="P59" s="3">
         <v>500</v>
       </c>
       <c r="Q59" s="3">
+        <v>500</v>
+      </c>
+      <c r="R59" s="3">
         <v>900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1400</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y59" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E60" s="3">
         <v>800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1500</v>
-      </c>
-      <c r="F60" s="3">
-        <v>3300</v>
       </c>
       <c r="G60" s="3">
         <v>3300</v>
       </c>
       <c r="H60" s="3">
+        <v>3300</v>
+      </c>
+      <c r="I60" s="3">
         <v>3700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>13800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>17500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>39900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2400</v>
       </c>
-      <c r="X60" s="3">
-        <v>0</v>
-      </c>
       <c r="Y60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4086,31 +4228,31 @@
         <v>600</v>
       </c>
       <c r="E61" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="F61" s="3">
         <v>700</v>
       </c>
       <c r="G61" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="H61" s="3">
         <v>800</v>
       </c>
       <c r="I61" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="J61" s="3">
         <v>900</v>
       </c>
       <c r="K61" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="L61" s="3">
         <v>1000</v>
       </c>
       <c r="M61" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="N61" s="3">
         <v>0</v>
@@ -4148,8 +4290,11 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4180,14 +4325,14 @@
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M62" s="3">
-        <v>1100</v>
+      <c r="M62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N62" s="3">
         <v>1100</v>
       </c>
       <c r="O62" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
@@ -4199,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="S62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T62" s="3">
         <v>100</v>
@@ -4207,8 +4352,8 @@
       <c r="U62" s="3">
         <v>100</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>4</v>
+      <c r="V62" s="3">
+        <v>100</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>4</v>
@@ -4219,8 +4364,11 @@
       <c r="Y62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4438,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4512,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,79 +4586,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E66" s="3">
         <v>1400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2200</v>
-      </c>
-      <c r="F66" s="3">
-        <v>4000</v>
       </c>
       <c r="G66" s="3">
         <v>4000</v>
       </c>
       <c r="H66" s="3">
+        <v>4000</v>
+      </c>
+      <c r="I66" s="3">
         <v>4500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5800</v>
-      </c>
-      <c r="J66" s="3">
-        <v>5200</v>
       </c>
       <c r="K66" s="3">
         <v>5200</v>
       </c>
       <c r="L66" s="3">
+        <v>5200</v>
+      </c>
+      <c r="M66" s="3">
         <v>4800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>17500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>39900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2400</v>
       </c>
-      <c r="X66" s="3">
-        <v>0</v>
-      </c>
       <c r="Y66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4690,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4762,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4836,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4743,8 +4910,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,79 +4984,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-43500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-41500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-37500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-36000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-34400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-32900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-30800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-28400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-26600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-22600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-19600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-16900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-13100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-5300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-3600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>4100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2700</v>
-      </c>
-      <c r="X72" s="3">
-        <v>-100</v>
       </c>
       <c r="Y72" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5132,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5206,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,79 +5280,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E76" s="3">
         <v>12600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>16300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2800</v>
       </c>
-      <c r="X76" s="3">
-        <v>0</v>
-      </c>
       <c r="Y76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5428,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E80" s="2">
         <v>45688</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45596</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45504</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45412</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45322</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45230</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45138</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45046</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44957</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44865</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44773</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44681</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44592</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44500</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44408</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44316</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44227</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44135</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44043</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43951</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43861</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43769</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-9000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1100</v>
       </c>
-      <c r="X81" s="3">
-        <v>0</v>
-      </c>
       <c r="Y81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,8 +5611,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5426,16 +5624,16 @@
         <v>200</v>
       </c>
       <c r="F83" s="3">
+        <v>200</v>
+      </c>
+      <c r="G83" s="3">
         <v>100</v>
       </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
       <c r="H83" s="3">
         <v>0</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>4</v>
+      <c r="I83" s="3">
+        <v>0</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>4</v>
@@ -5464,8 +5662,8 @@
       <c r="R83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
+      <c r="S83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
@@ -5485,8 +5683,11 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5757,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5831,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5905,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5979,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,79 +6053,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-9300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-5400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2000</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
       <c r="Y89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,8 +6157,9 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5958,8 +6178,8 @@
       <c r="H91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -6009,8 +6229,11 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6303,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,8 +6377,11 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6171,20 +6400,20 @@
       <c r="H94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
+      <c r="I94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-300</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>4</v>
+      <c r="M94" s="3">
+        <v>0</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>4</v>
@@ -6201,8 +6430,8 @@
       <c r="R94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
+      <c r="S94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
@@ -6222,8 +6451,11 @@
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,8 +6481,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6281,8 +6514,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6320,8 +6553,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6627,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6701,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,64 +6775,67 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>500</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>1500</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>9700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>4</v>
+      <c r="U100" s="3">
+        <v>0</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>4</v>
@@ -6604,8 +6849,11 @@
       <c r="Y100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6636,8 +6884,8 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -6675,75 +6923,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-5500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>4800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2000</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
       <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>0</v>
       </c>
     </row>
